--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512412_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512412_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9801</v>
+        <v>6.1034</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9181</v>
+        <v>4.3057</v>
       </c>
       <c r="F2" t="n">
-        <v>2.062</v>
+        <v>1.7976</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5085</v>
+        <v>6.5389</v>
       </c>
       <c r="H2" t="n">
-        <v>2.734</v>
+        <v>2.7094</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7746</v>
+        <v>3.8295</v>
       </c>
       <c r="J2" t="n">
-        <v>5.493</v>
+        <v>5.5935</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2052</v>
+        <v>2.2323</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2878</v>
+        <v>3.3611</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0155</v>
+        <v>0.9454</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5288</v>
+        <v>0.4771</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1559</v>
+        <v>-0.0791</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3587</v>
+        <v>-0.1093</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2028</v>
+        <v>0.0302</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.014</v>
+        <v>2.9571</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5235</v>
+        <v>1.6681</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4904</v>
+        <v>1.289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2779</v>
+        <v>0.8408</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8556</v>
+        <v>-3.4394</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1335</v>
+        <v>4.2802</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2083</v>
+        <v>0.3155</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.855</v>
+        <v>-3.7377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6468</v>
+        <v>4.0532</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4862</v>
+        <v>0.5253</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.2983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4868</v>
+        <v>0.2269</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4097</v>
+        <v>1.6196</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3748</v>
+        <v>-0.1916</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0094</v>
+        <v>0.1624</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3654</v>
+        <v>-0.354</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7709</v>
+        <v>0.6883</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7709</v>
+        <v>1.1902</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2585</v>
+        <v>2.66</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0586</v>
+        <v>0.5004</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3171</v>
+        <v>2.1596</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1586</v>
+        <v>0.2777</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9194</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2392</v>
+        <v>1.1279</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1589</v>
+        <v>-0.153</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3903</v>
+        <v>-0.8126</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5492</v>
+        <v>0.6596</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3174</v>
+        <v>0.4307</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5291</v>
+        <v>-0.0376</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7884</v>
+        <v>0.4684</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4339</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4339</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.334</v>
+        <v>1.0019</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1003</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4343</v>
+        <v>0.1093</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.7853</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7853</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4308</v>
+        <v>2.3778</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2322</v>
+        <v>0.0663</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1986</v>
+        <v>2.3116</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8016</v>
+        <v>1.1281</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.4368</v>
+        <v>0.891</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2384</v>
+        <v>0.2371</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2138</v>
+        <v>-0.1307</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.7707</v>
+        <v>0.3951</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9846</v>
+        <v>-0.5258</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5878</v>
+        <v>1.2588</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3339</v>
+        <v>0.4959</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2539</v>
+        <v>0.7629</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6388</v>
+        <v>1.4172</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7061</v>
+        <v>-0.1674</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1622</v>
+        <v>0.197</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5438</v>
+        <v>-0.3644</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2685</v>
+        <v>1.522</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1818</v>
+        <v>0.2468</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0867</v>
+        <v>1.2752</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8405</v>
+        <v>0.8252</v>
       </c>
       <c r="H6" t="n">
-        <v>2.107</v>
+        <v>2.0959</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2666</v>
+        <v>-1.2707</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7165</v>
+        <v>0.7506</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9125</v>
+        <v>1.936</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1959</v>
+        <v>-1.1854</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1239</v>
+        <v>0.0746</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1946</v>
+        <v>0.1599</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0706</v>
+        <v>-0.0853</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2103</v>
+        <v>0.4581</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6814</v>
+        <v>0.6747</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4711</v>
+        <v>-0.2166</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4161</v>
+        <v>0.7577</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7678</v>
+        <v>-0.3209</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1838</v>
+        <v>1.0786</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3368</v>
+        <v>0.3396</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2374</v>
+        <v>1.2261</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9006</v>
+        <v>-0.8865</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0432</v>
+        <v>-0.0129</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6322</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6677</v>
+        <v>-0.6451</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38</v>
+        <v>0.3526</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6129</v>
+        <v>0.594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2329</v>
+        <v>-0.2414</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.187</v>
+        <v>0.1549</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3763</v>
+        <v>0.0362</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1893</v>
+        <v>0.1187</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0377</v>
+        <v>-0.4205</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3087</v>
+        <v>1.3648</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3464</v>
+        <v>-1.7853</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4375</v>
+        <v>2.4286</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8759</v>
+        <v>1.8778</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5616</v>
+        <v>0.5508</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7788</v>
+        <v>1.7992</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5417</v>
+        <v>1.5606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2371</v>
+        <v>0.2385</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6587</v>
+        <v>0.6294</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3342</v>
+        <v>0.3171</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6812</v>
+        <v>0.3289</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3121</v>
+        <v>0.327</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3691</v>
+        <v>0.0019</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.9515</v>
+        <v>-2.9755</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.1936</v>
+        <v>-3.2264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2824</v>
+        <v>-0.9055</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6314</v>
+        <v>-1.0236</v>
       </c>
       <c r="F9" t="n">
-        <v>0.349</v>
+        <v>0.1182</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7113</v>
+        <v>0.3678</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8111</v>
+        <v>0.3165</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5224</v>
+        <v>0.0513</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9697</v>
+        <v>-0.594</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2262</v>
+        <v>-0.2977</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1959</v>
+        <v>-0.2963</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2584</v>
+        <v>0.9618</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5849</v>
+        <v>0.6141</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3264</v>
+        <v>0.3477</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6145</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-3.0368</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.8221</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4047</v>
+        <v>0.2856</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0833</v>
+        <v>0.5708</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3214</v>
+        <v>-0.2853</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3612</v>
+        <v>-0.3442</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6965</v>
+        <v>2.0362</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6647</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4978</v>
+        <v>-2.245</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3658</v>
+        <v>-2.3643</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.132</v>
+        <v>0.1193</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3432</v>
+        <v>-0.7194</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3205</v>
+        <v>0.8105</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0227</v>
+        <v>-1.5298</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3202</v>
+        <v>0.2555</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3476</v>
+        <v>-1.1854</v>
       </c>
       <c r="M10" t="n">
-        <v>1.011</v>
+        <v>0.2106</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6407</v>
+        <v>0.555</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3703</v>
+        <v>-0.3444</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2291</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0727</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8436</v>
+        <v>1.4172</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2636</v>
+        <v>1.4621</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6383</v>
+        <v>1.2785</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6254</v>
+        <v>0.1836</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3482</v>
+        <v>-2.3804</v>
       </c>
       <c r="W10" t="n">
-        <v>2.013</v>
+        <v>-0.6883</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3612</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.5501</v>
+        <v>12.807</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3407</v>
+        <v>4.4433</v>
       </c>
       <c r="F11" t="n">
-        <v>9.209200000000001</v>
+        <v>8.363799999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>11.9933</v>
+        <v>12.0273</v>
       </c>
       <c r="H11" t="n">
-        <v>5.7129</v>
+        <v>5.6375</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2804</v>
+        <v>6.389800000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>6.1542</v>
+        <v>6.6383</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9545</v>
+        <v>2.1637</v>
       </c>
       <c r="L11" t="n">
-        <v>4.199999999999999</v>
+        <v>4.474400000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>5.8389</v>
+        <v>5.3892</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7585</v>
+        <v>3.4738</v>
       </c>
       <c r="O11" t="n">
-        <v>2.0808</v>
+        <v>1.9154</v>
       </c>
       <c r="P11" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.2909</v>
+        <v>-12.1471</v>
       </c>
       <c r="R11" t="n">
-        <v>12.2907</v>
+        <v>12.1473</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0244</v>
+        <v>3.2534</v>
       </c>
       <c r="T11" t="n">
-        <v>1.651</v>
+        <v>4.0299</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6265999999999999</v>
+        <v>-0.7766</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.467199999999999</v>
+        <v>-2.4738</v>
       </c>
       <c r="W11" t="n">
-        <v>5.8267</v>
+        <v>5.9221</v>
       </c>
       <c r="X11" t="n">
-        <v>-8.293900000000001</v>
+        <v>-8.395899999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.1884</v>
+        <v>4.0799</v>
       </c>
       <c r="E12" t="n">
-        <v>4.634</v>
+        <v>4.3823</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4456</v>
+        <v>-0.3023</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7716</v>
+        <v>2.7942</v>
       </c>
       <c r="H12" t="n">
-        <v>1.821</v>
+        <v>1.8751</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9506</v>
+        <v>0.919</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0448</v>
+        <v>3.1493</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7658</v>
+        <v>1.8536</v>
       </c>
       <c r="L12" t="n">
-        <v>1.279</v>
+        <v>1.2957</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2732</v>
+        <v>-0.3551</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0552</v>
+        <v>0.0215</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3284</v>
+        <v>-0.3766</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9456</v>
+        <v>0.8202</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6005</v>
+        <v>0.209</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3451</v>
+        <v>0.6112</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="W12" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8612</v>
+        <v>1.8537</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1037</v>
+        <v>-0.2253</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9649</v>
+        <v>2.0791</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2501</v>
+        <v>0.2661</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9343</v>
+        <v>0.9669</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6842</v>
+        <v>-0.7008</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0396</v>
+        <v>0.0275</v>
       </c>
       <c r="K13" t="n">
-        <v>0.154</v>
+        <v>0.1956</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1935</v>
+        <v>-0.168</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2897</v>
+        <v>0.2386</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7803</v>
+        <v>0.7714</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4906</v>
+        <v>-0.5327</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2143</v>
+        <v>0.2189</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.2529</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2785</v>
+        <v>0.4718</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4846</v>
+        <v>0.9032</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5142</v>
+        <v>1.9373</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0296</v>
+        <v>-1.034</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.674</v>
+        <v>-1.6881</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9087</v>
+        <v>-0.9093</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7653</v>
+        <v>-0.7788</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.065</v>
+        <v>-0.0401</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1836</v>
+        <v>-0.1594</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6089</v>
+        <v>-1.648</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7251</v>
+        <v>-0.7499</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5068</v>
+        <v>-0.0645</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1566</v>
+        <v>0.5362</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6498</v>
+        <v>-0.6007</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4818</v>
+        <v>-0.4582</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9161</v>
+        <v>-1.163</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4342</v>
+        <v>0.7048</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9035</v>
+        <v>-0.9429</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3068</v>
+        <v>-0.3158</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5968</v>
+        <v>-0.6271</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4226</v>
+        <v>-0.415</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5016</v>
+        <v>-0.4945</v>
       </c>
       <c r="L15" t="n">
-        <v>0.079</v>
+        <v>0.0795</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4809</v>
+        <v>-0.5278</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1949</v>
+        <v>0.1787</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6758</v>
+        <v>-0.7066</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0233</v>
+        <v>0.0558</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1323</v>
+        <v>-0.1646</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1091</v>
+        <v>0.2204</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.762</v>
+        <v>-0.5649</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2241</v>
+        <v>0.3124</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9861</v>
+        <v>-0.8773</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2316</v>
+        <v>0.242</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2737</v>
+        <v>1.2655</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0421</v>
+        <v>-1.0235</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0009</v>
+        <v>0.0516</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9953</v>
+        <v>1.0075</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9943</v>
+        <v>-0.9559</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2307</v>
+        <v>0.1904</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2784</v>
+        <v>0.258</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0477</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2227</v>
+        <v>-0.0217</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0668</v>
+        <v>0.0828</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2895</v>
+        <v>-0.1045</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3612</v>
+        <v>-2.3804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4558</v>
+        <v>-0.764</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09760000000000001</v>
+        <v>-1.9593</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5535</v>
+        <v>1.1953</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0199</v>
+        <v>-0.3676</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5104</v>
+        <v>0.099</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5095</v>
+        <v>-0.4666</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1381</v>
+        <v>0.6382</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0195</v>
+        <v>0.7105</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1185</v>
+        <v>-0.0723</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.158</v>
+        <v>-1.0058</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5299</v>
+        <v>-0.6115</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.628</v>
+        <v>-0.3943</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4097</v>
+        <v>1.8221</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8456</v>
+        <v>-0.5381</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0404</v>
+        <v>-0.573</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8052</v>
+        <v>0.0349</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8808</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6769</v>
+        <v>0.5213</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7962</v>
+        <v>-1.3928</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3377</v>
+        <v>-1.0523</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1031</v>
+        <v>-0.5326</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4408</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6888</v>
+        <v>0.0198</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0895</v>
+        <v>0.1193</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-1.1913</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5857</v>
+        <v>-0.5523</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3513</v>
+        <v>-0.639</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2048</v>
+        <v>0.4049</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8436</v>
+        <v>0.4049</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6864</v>
+        <v>-0.2241</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2277</v>
+        <v>0.3823</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4587</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3482</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.3594</v>
+        <v>-4.8235</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0927</v>
+        <v>-3.6557</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2667</v>
+        <v>-1.1678</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.6274</v>
+        <v>-7.6269</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.6824</v>
+        <v>-4.6659</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.9449</v>
+        <v>-2.961</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.9475</v>
+        <v>-4.8748</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.0967</v>
+        <v>-4.0544</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8508</v>
+        <v>-0.8204</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6799</v>
+        <v>-2.7521</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5857</v>
+        <v>-0.6115</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0941</v>
+        <v>-2.1407</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4657</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4822</v>
+        <v>-0.149</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0165</v>
+        <v>0.2157</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1191</v>
+        <v>2.1295</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.144500000000001</v>
+        <v>-7.8444</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.889900000000001</v>
+        <v>-8.5136</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7454</v>
+        <v>0.6692</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6841</v>
+        <v>-3.6518</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.4365</v>
+        <v>-3.4205</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2476</v>
+        <v>-0.2313</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.1474</v>
+        <v>-4.0649</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.5998</v>
+        <v>-2.5524</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5475</v>
+        <v>-1.5125</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4633</v>
+        <v>0.413</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8367</v>
+        <v>-0.8682</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.2812</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.8921</v>
+        <v>-3.8466</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5061</v>
+        <v>0.7509</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4849</v>
+        <v>0.7057</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0212</v>
+        <v>0.0452</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0744</v>
+        <v>-1.097</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1062</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-1.0037</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.5501</v>
+        <v>-8.489699999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.209399999999999</v>
+        <v>-8.3636</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3408</v>
+        <v>-0.1257999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-11.9933</v>
+        <v>-12.0273</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.7127</v>
+        <v>-5.637599999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.280600000000001</v>
+        <v>-6.3898</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.839</v>
+        <v>-5.389199999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.758300000000001</v>
+        <v>-3.4737</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0806</v>
+        <v>-1.9153</v>
       </c>
       <c r="M21" t="n">
-        <v>-6.154199999999999</v>
+        <v>-6.6381</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9543</v>
+        <v>-2.1638</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.199700000000001</v>
+        <v>-4.4744</v>
       </c>
       <c r="P21" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-12.2908</v>
+        <v>-12.1472</v>
       </c>
       <c r="R21" t="n">
-        <v>12.2908</v>
+        <v>12.1472</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0243</v>
+        <v>1.064</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6266000000000002</v>
+        <v>0.7765</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.651</v>
+        <v>0.2876</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4674</v>
+        <v>2.473600000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>8.294</v>
+        <v>8.395800000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-5.826600000000001</v>
+        <v>-5.9221</v>
       </c>
     </row>
   </sheetData>
